--- a/leagues.xlsx
+++ b/leagues.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\petrm\Documents\Python\fmscouts_footy_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0627812-5248-4932-A1CE-001DE9351F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5DCF93-1851-47FD-82EC-526504BF193D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB2E288D-BBEE-4D54-A17D-9E55B0FF3441}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{EB2E288D-BBEE-4D54-A17D-9E55B0FF3441}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>aus1</t>
   </si>
@@ -112,6 +112,33 @@
   </si>
   <si>
     <t>srb2</t>
+  </si>
+  <si>
+    <t>k hovnu</t>
+  </si>
+  <si>
+    <t>potenciální ligy</t>
+  </si>
+  <si>
+    <t>arménie</t>
+  </si>
+  <si>
+    <t>albánie</t>
+  </si>
+  <si>
+    <t>gruzie</t>
+  </si>
+  <si>
+    <t>kosovo</t>
+  </si>
+  <si>
+    <t>černá hora</t>
+  </si>
+  <si>
+    <t>švýcarsko</t>
+  </si>
+  <si>
+    <t>ukrajina</t>
   </si>
 </sst>
 </file>
@@ -464,132 +491,165 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EAB45A7-1ED7-4A7B-B173-A0241DE138FE}">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
